--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +490,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1460,6 +1462,7 @@
       </c>
       <c r="H34" s="6" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
@@ -1479,6 +1482,15 @@
       <formula1>"Pendiente,En Curso,Completado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing Pre-Apertura" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Marketing Pre-Apertura'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Marketing Pre-Apertura'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +61,25 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +96,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,10 +152,73 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+          <bgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -492,16 +580,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Checklist Marketing Pre-Apertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Instrucciones de uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Rellena las celdas verdes con tus datos; el resto lo calcula el libro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Las hojas están protegidas SIN contraseña para que una copia accidental no borre una fórmula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Para editar la estructura o una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -576,21 +761,21 @@
           <t>Nombre del restaurante y registro de marca</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Propietario</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -606,21 +791,21 @@
           <t>Diseño de logo y branding profesional</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Diseñador</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="H6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -636,21 +821,21 @@
           <t>Línea gráfica: carta, tarjetas, uniformes, señalética</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Diseñador</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n">
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -666,21 +851,21 @@
           <t>Historia/narrativa del chef y del restaurante</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Chef + Marketing</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="H8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -696,21 +881,21 @@
           <t>Web propia optimizada SEO (restaurante + ciudad)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Agencia web</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n">
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="H9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -726,21 +911,21 @@
           <t>Perfil Google My Business completo y verificado</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="n"/>
+      <c r="H10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -756,21 +941,21 @@
           <t>Instagram: perfil profesional con grid planificado</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="n"/>
+      <c r="H11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -783,24 +968,28 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Sesión de fotos profesional de platos (15-25 platos)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+          <t>Sesión de fotos profesional de platos (15‑25 platos)</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Fotógrafo</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H12" s="6" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Rango real 1.500‑3.000 € (SPEC §3.4). Va precargado el MÍNIMO: ajústalo con presupuesto. Los 500 € anteriores no compraban fotografía gastronómica profesional y contradecían el propio rango de lanzamiento de 5.000‑30.000 € del libro.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -813,24 +1002,24 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Vídeo del restaurante y cocina (60-90 segundos)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+          <t>Vídeo del restaurante y cocina (60‑90 segundos)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Videógrafo</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n">
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="H13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -846,21 +1035,21 @@
           <t>Perfil en TheFork/ElTenedor optimizado</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Maître</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="n"/>
+      <c r="H14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -876,21 +1065,21 @@
           <t>Perfil en TripAdvisor reclamado</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="n"/>
+      <c r="H15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -898,29 +1087,31 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PR/Prensa</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Nota de prensa profesional para medios</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Agencia PR</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H16" s="6" t="n"/>
+          <t>Sesión de fotos del equipo, la sala y la cocina (no solo platos)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Fotógrafo</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>La prensa gastronómica pide retrato de chef y de sala; sin ellas la nota de prensa sale sin foto. Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -928,29 +1119,31 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>PR/Prensa</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Envío a medios gastronómicos (El Comidista, Bon Viveur)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Agencia PR</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n"/>
+          <t>Página de reservas propia con seguimiento de origen (UTM) y confirmación por email</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Agencia web</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Sin UTM no se sabe qué canal trae reservas y todo el presupuesto de lanzamiento se gasta a ciegas.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -963,24 +1156,24 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Envío a medios locales y regionales</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+          <t>Nota de prensa profesional para medios</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Agencia PR</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="H18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -993,24 +1186,24 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Invitación a 5-10 periodistas/influencers gastronómicos</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H19" s="6" t="n"/>
+          <t>Envío a medios gastronómicos (El Comidista, Bon Viveur)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Agencia PR</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1023,24 +1216,24 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Contratar agencia de comunicación gastronómica</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Propietario</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H20" s="6" t="n"/>
+          <t>Envío a medios locales y regionales</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Agencia PR</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1048,29 +1241,29 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>PR/Prensa</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Evento de pre-apertura (prensa + amigos + industria)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H21" s="6" t="n"/>
+          <t>Invitación a 5‑10 periodistas/influencers gastronómicos</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1078,29 +1271,29 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>PR/Prensa</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Soft opening: 2 semanas de servicio de prueba</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Chef + Maître</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n"/>
+          <t>Contratar agencia de comunicación gastronómica</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Propietario</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1108,29 +1301,31 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>PR/Prensa</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Planificar participación en Madrid Fusión / Gastronomika</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H23" s="6" t="n"/>
+          <t>Dossier de prensa y kit de imágenes en alta resolución descargable</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Agencia PR</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Sin importe tasado en la guía: pide presupuesto y escríbelo aquí (la celda es editable y el TOTAL se recalcula).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1143,24 +1338,24 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Colaboraciones con productores locales (eventos Km0)</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H24" s="6" t="n"/>
+          <t>Evento de pre-apertura (prensa + amigos + industria)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1168,29 +1363,29 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Reservas</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Sistema de reservas configurado (Tock/Resy/TheFork)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Maître</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>500</v>
-      </c>
-      <c r="H25" s="6" t="n"/>
+          <t>Soft opening: 2 semanas de servicio de prueba</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Chef + Maître</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1198,29 +1393,29 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Reservas</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Política de reservas, cancelación y no-show definida</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Maître</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n"/>
+          <t>Planificar participación en Madrid Fusión / Gastronomika</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1228,29 +1423,29 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Reservas</t>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Protocolo de gestión de lista de espera</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Hostess</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n"/>
+          <t>Colaboraciones con productores locales (eventos Km0)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="H27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1258,29 +1453,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Guías</t>
+          <t>Reservas</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Informar a la Guía Michelin de la apertura</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n"/>
+          <t>Sistema de reservas configurado (Tock, TheFork, Cover Manager o Restoo)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Maître</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>Resy fuera: no opera en España y era la única cifra en dólares de todo el producto (300‑500 USD/mes). Las cuatro alternativas sí están disponibles aquí y facturan en euros.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1288,29 +1487,29 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Guías</t>
+          <t>Reservas</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Informar a la Guía Repsol de la apertura</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Chef</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n">
+          <t>Política de reservas, cancelación y no-show definida</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Maître</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="n"/>
+      <c r="H29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1318,29 +1517,29 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Guías</t>
+          <t>Reservas</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Enviar información a guías locales y regionales</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="n">
+          <t>Protocolo de gestión de lista de espera</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Hostess</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1348,29 +1547,29 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Fidelización</t>
+          <t>Guías</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Base de datos de clientes (CRM básico)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n">
+          <t>Informar a la Guía Michelin de la apertura</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="n"/>
+      <c r="H31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1378,29 +1577,29 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Fidelización</t>
+          <t>Guías</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Newsletter mensual / trimestral</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="n">
+          <t>Informar a la Guía Repsol de la apertura</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Chef</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="n"/>
+      <c r="H32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1408,29 +1607,29 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Fidelización</t>
+          <t>Guías</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Programa de recomendación boca a boca</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Maître</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="n">
+          <t>Enviar información a guías locales y regionales</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="n"/>
+      <c r="H33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1443,43 +1642,374 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
+          <t>Base de datos de clientes (CRM básico)</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Newsletter mensual / trimestral</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Programa de recomendación boca a boca</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Maître</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
           <t>Seguimiento de reseñas online (responder todas)</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n">
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="H37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Medición</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Presupuesto de lanzamiento repartido por canal y por mes</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>El libro maneja un rango de lanzamiento de 5.000‑30.000 €: repártelo antes de gastarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Medición</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Cuadro de mando: reservas por origen y coste de captación por cliente</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="15" t="n"/>
+      <c r="G40" s="16" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>RESUMEN — lo calcula el libro (v2.0)</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL PRESUPUESTADO (€)</t>
+        </is>
+      </c>
+      <c r="G42" s="20">
+        <f>SUM(G5:G39)</f>
+        <v>23800.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Partidas SIN importe (a presupuestar)</t>
+        </is>
+      </c>
+      <c r="G43" s="21">
+        <f>COUNTIF(B5:B39,"&lt;&gt;")-COUNT(G5:G39)</f>
+        <v>5.0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Avance del checklist (% completado)</t>
+        </is>
+      </c>
+      <c r="F44" s="22">
+        <f>IFERROR(COUNTIF(F5:F39,"Completado")/COUNTIF(F5:F39,"&lt;&gt;"),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Estado terminal de este checklist: «Completado»</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>SUBTOTALES POR CATEGORÍA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Identidad</t>
+        </is>
+      </c>
+      <c r="G47" s="16">
+        <f>SUMIF($B$5:$B$39,$A47,$G$5:$G$39)</f>
+        <v>5300.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="G48" s="16">
+        <f>SUMIF($B$5:$B$39,$A48,$G$5:$G$39)</f>
+        <v>7000.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PR/Prensa</t>
+        </is>
+      </c>
+      <c r="G49" s="16">
+        <f>SUMIF($B$5:$B$39,$A49,$G$5:$G$39)</f>
+        <v>5500.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="G50" s="16">
+        <f>SUMIF($B$5:$B$39,$A50,$G$5:$G$39)</f>
+        <v>5500.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Reservas</t>
+        </is>
+      </c>
+      <c r="G51" s="16">
+        <f>SUMIF($B$5:$B$39,$A51,$G$5:$G$39)</f>
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guías</t>
+        </is>
+      </c>
+      <c r="G52" s="16">
+        <f>SUMIF($B$5:$B$39,$A52,$G$5:$G$39)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="G53" s="16">
+        <f>SUMIF($B$5:$B$39,$A53,$G$5:$G$39)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Medición</t>
+        </is>
+      </c>
+      <c r="G54" s="16">
+        <f>SUMIF($B$5:$B$39,$A54,$G$5:$G$39)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:H4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A56:H56"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="F5:F39">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+      <formula>"Completado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"En Curso"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>"Pendiente"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43">
+    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(G43),G43&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha no válida" error="Escribe una fecha (dd/mm/aaaa) entre 2020 y 2040." type="date" operator="between">
+      <formula1>DATE(2020,1,1)</formula1>
+      <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista: Pendiente, En Curso, Completado" type="list">
       <formula1>"Pendiente,En Curso,Completado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-marketing-preapertura.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +177,10 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1830,147 +1834,236 @@
       <c r="H41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>TOTAL PRESUPUESTADO (€)</t>
         </is>
       </c>
-      <c r="G42" s="20">
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="23">
         <f>SUM(G5:G39)</f>
         <v>23800.0</v>
       </c>
+      <c r="H42" s="18" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>Partidas SIN importe (a presupuestar)</t>
         </is>
       </c>
-      <c r="G43" s="21">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="24">
         <f>COUNTIF(B5:B39,"&lt;&gt;")-COUNT(G5:G39)</f>
         <v>5.0</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Avance del checklist (% completado)</t>
         </is>
       </c>
-      <c r="F44" s="22">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="25">
         <f>IFERROR(COUNTIF(F5:F39,"Completado")/COUNTIF(F5:F39,"&lt;&gt;"),"")</f>
         <v>0.0</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>Estado terminal de este checklist: «Completado»</t>
         </is>
       </c>
-    </row>
-    <row r="45"/>
+      <c r="H44" s="18" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+    </row>
     <row r="46">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>SUBTOTALES POR CATEGORÍA</t>
         </is>
       </c>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="18" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Identidad</t>
         </is>
       </c>
-      <c r="G47" s="16">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="26">
         <f>SUMIF($B$5:$B$39,$A47,$G$5:$G$39)</f>
         <v>5300.0</v>
       </c>
+      <c r="H47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
-      <c r="G48" s="16">
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="26">
         <f>SUMIF($B$5:$B$39,$A48,$G$5:$G$39)</f>
         <v>7000.0</v>
       </c>
+      <c r="H48" s="18" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>PR/Prensa</t>
         </is>
       </c>
-      <c r="G49" s="16">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="26">
         <f>SUMIF($B$5:$B$39,$A49,$G$5:$G$39)</f>
         <v>5500.0</v>
       </c>
+      <c r="H49" s="18" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
       </c>
-      <c r="G50" s="16">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="26">
         <f>SUMIF($B$5:$B$39,$A50,$G$5:$G$39)</f>
         <v>5500.0</v>
       </c>
+      <c r="H50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="G51" s="16">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="26">
         <f>SUMIF($B$5:$B$39,$A51,$G$5:$G$39)</f>
         <v>500.0</v>
       </c>
+      <c r="H51" s="18" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Guías</t>
         </is>
       </c>
-      <c r="G52" s="16">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="26">
         <f>SUMIF($B$5:$B$39,$A52,$G$5:$G$39)</f>
         <v>0.0</v>
       </c>
+      <c r="H52" s="18" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>Fidelización</t>
         </is>
       </c>
-      <c r="G53" s="16">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="26">
         <f>SUMIF($B$5:$B$39,$A53,$G$5:$G$39)</f>
         <v>0.0</v>
       </c>
+      <c r="H53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>Medición</t>
         </is>
       </c>
-      <c r="G54" s="16">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="26">
         <f>SUMIF($B$5:$B$39,$A54,$G$5:$G$39)</f>
         <v>0.0</v>
       </c>
-    </row>
-    <row r="55"/>
+      <c r="H54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="n"/>
+    </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
@@ -1985,13 +2078,13 @@
     <mergeCell ref="A56:H56"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F39">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
       <formula>"Completado"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"En Curso"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
